--- a/engineering/PnP.xlsx
+++ b/engineering/PnP.xlsx
@@ -5,7 +5,7 @@
     <workbookView showHorizontalScroll="0"/>
   </bookViews>
   <sheets>
-    <sheet name="PnP" sheetId="1" r:id="R154ef9f43ace4956"/>
+    <sheet name="PnP" sheetId="1" r:id="Rdccbea184173421f"/>
   </sheets>
 </workbook>
 </file>
@@ -186,17 +186,23 @@
     </comment>
     <comment ref="C15" authorId="0">
       <text>
-        <t>C17,C20: Panasonic EEHZS1H221P. Footprint: CP_Elec_Panasonic_G16_10x16.5_ZS. Two parallel capacitors per PCB. 440 uF nominal bank; verify polarity, thermal/ripple performance and installed ESC transient behavior.</t>
+        <r>
+          <t>C17,C20: Panasonic EEHZS1H221P. Footprint: CP_Elec_Panasonic_G16_10x16.5_ZS. Two parallel capacitors per PCB. 440 uF nominal bank; verify polarity, thermal/ripple performance and installed ESC transient behavior.</t>
+        </r>
       </text>
     </comment>
     <comment ref="E15" authorId="0">
       <text>
-        <t>Passive; 2 fitted per PCB. Spare policy retained. Order multiple 1.</t>
+        <r>
+          <t>Passive; 2 fitted per PCB. Spare policy retained. Order multiple 1.</t>
+        </r>
       </text>
     </comment>
     <comment ref="F15" authorId="0">
       <text>
-        <t>LCSC reference price and stock checked October 15, 2026. Source: https://www.lcsc.com/product-detail/C385885.html. Actual checkout governs final price.</t>
+        <r>
+          <t>LCSC reference price and stock checked October 15, 2026. Source: https://www.lcsc.com/product-detail/C385885.html. Actual checkout governs final price.</t>
+        </r>
       </text>
     </comment>
     <comment ref="C16" authorId="0">
@@ -229,30 +235,17 @@
     </comment>
     <comment ref="C17" authorId="0">
       <text>
-        <r>
-          <t>Manufacturer: Bourns
-Exact MPN: SMAJ24CA
-References: D1,D4
-Footprint: D_SMA
-Packaging: Confirm packaging with assembler
-Supplier: DigiKey
-Stock snapshot: October 15, 2026.
-Stock snapshot checked 2026-10-15; checkout may differ.</t>
-        </r>
+        <t>D1,D4: RUILON SMAJ24CA. Footprint: D_SMA. SMAJ24CA bidirectional SMA replacement, same nominal protection ratings; public JLC stock snapshot 3698, five-board fitted need 10 plus catalog loss 4.</t>
       </text>
     </comment>
     <comment ref="E17" authorId="0">
       <text>
-        <r>
-          <t>Part class: Other. Supplier order multiple: 1. </t>
-        </r>
+        <t>Other; 2 fitted per PCB. Spare policy retained. Order multiple 10.</t>
       </text>
     </comment>
     <comment ref="F17" authorId="0">
       <text>
-        <r>
-          <t>Price basis: 2026-10-05 estimate. Reference / estimated unit price, not a current quote. Supplier: DigiKey. https://www.digikey.com/en/products/detail/bourns-inc/SMAJ24CA/2254533</t>
-        </r>
+        <t>Supplier reference price and stock checked October 15, 2026. Source: https://www.lcsc.com/product-detail/C28092.html. Actual checkout governs final price.</t>
       </text>
     </comment>
     <comment ref="C18" authorId="0">
@@ -873,30 +866,17 @@
     </comment>
     <comment ref="C40" authorId="0">
       <text>
-        <r>
-          <t>Manufacturer: Vishay
-Exact MPN: CRCW25121K00FKEGHP
-References: R19
-Footprint: R_2512_6332Metric
-Packaging: Cut tape / custom reel; leaders
-Supplier: DigiKey
-Stock snapshot: October 15, 2026.
-Normalize CAD ordering code to procurement/distributor MPN for same intended 1 kOhm CRCW-HP part. Do not use pasted 1 W 5% UNI-ROYAL selection.</t>
-        </r>
+        <t>R19: Vishay CRCW25121K00FKEGHP. Footprint: R_2512_6332Metric. Exact Vishay MPN match. Public JLC stock 2; five-board need 5, short 3. Global sourcing/private inventory required.</t>
       </text>
     </comment>
     <comment ref="E40" authorId="0">
       <text>
-        <r>
-          <t>Part class: Passive. Supplier order multiple: 1. </t>
-        </r>
+        <t>Passive; 1 fitted per PCB. Spare policy retained. Order multiple 1.</t>
       </text>
     </comment>
     <comment ref="F40" authorId="0">
       <text>
-        <r>
-          <t>Price basis: 2026-10-15 reference. Reference / estimated unit price, not a current quote. Supplier: DigiKey. https://www.digikey.com/en/products/detail/vishay-dale/CRCW25121K00FKEGHP/2222092</t>
-        </r>
+        <t>Supplier reference price and stock checked October 15, 2026. Source: https://www.digikey.com/en/products/detail/vishay-dale/CRCW25121K00FKEGHP/2222612. Actual checkout governs final price.</t>
       </text>
     </comment>
     <comment ref="C41" authorId="0">
@@ -985,17 +965,23 @@
     </comment>
     <comment ref="C44" authorId="0">
       <text>
-        <t>U2: Texas Instruments INA238AIDGSR. Footprint: VSSOP10_DGS_TEX. INA238 16-bit U2. Use updated INA238 firmware. Same DGS footprint and pinout as former INA228.</t>
+        <r>
+          <t>U2: Texas Instruments INA238AIDGSR. Footprint: VSSOP10_DGS_TEX. INA238 16-bit U2. Use updated INA238 firmware. Same DGS footprint and pinout as former INA228.</t>
+        </r>
       </text>
     </comment>
     <comment ref="E44" authorId="0">
       <text>
-        <t>IC; 1 fitted per PCB. Spare policy retained. Order multiple 1.</t>
+        <r>
+          <t>IC; 1 fitted per PCB. Spare policy retained. Order multiple 1.</t>
+        </r>
       </text>
     </comment>
     <comment ref="F44" authorId="0">
       <text>
-        <t>LCSC reference price and stock checked October 15, 2026. Source: https://www.lcsc.com/product-detail/C2868250.html. Actual checkout governs final price.</t>
+        <r>
+          <t>LCSC reference price and stock checked October 15, 2026. Source: https://www.lcsc.com/product-detail/C2868250.html. Actual checkout governs final price.</t>
+        </r>
       </text>
     </comment>
     <comment ref="C45" authorId="0">
@@ -1668,7 +1654,7 @@
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="10" t="str">
-        <v>Updated U2 and C17/C20. Assembly and service quotes are still needed. Confirm stock at checkout.</v>
+        <v>D1/D4: RUILON C28092. R19: exact C4265875. JLC shortages remain; service costs need quotes.</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -1689,7 +1675,7 @@
       <c r="C5" s="2"/>
       <c r="D5" s="13" t="n">
         <f>SUM(H9:H48)</f>
-        <v>788.8374</v>
+        <v>785.7914000000002</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="2" t="str">
@@ -1698,7 +1684,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="13" t="n">
         <f>SUM(G9:G48)</f>
-        <v>57.84179999999999</v>
+        <v>57.2316</v>
       </c>
       <c r="I5" s="2" t="str">
         <v>Full build cost</v>
@@ -1717,7 +1703,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="13" t="n">
         <f>D5/$B$3</f>
-        <v>157.76748</v>
+        <v>157.15828000000005</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="2" t="str">
@@ -2115,7 +2101,7 @@
       </c>
       <c r="B17" s="23" t="str">
         <v>SMAJ24CA
-Bourns</v>
+RUILON</v>
       </c>
       <c r="C17" s="23" t="str">
         <v>SMAJ24CA</v>
@@ -2124,22 +2110,23 @@
         <v>2</v>
       </c>
       <c r="E17" s="28" t="n">
-        <f>CEILING(MAX(ROUNDUP(D17*$B$3*(1+$D$3),0),0),1)</f>
-        <v>12</v>
+        <f>CEILING(D17*$B$3*(1+$D$3),10)</f>
+        <v>20</v>
       </c>
       <c r="F17" s="30" t="n">
-        <v>0.382</v>
+        <f>IF(E17&gt;=10000,0.0403,IF(E17&gt;=5000,0.0427,IF(E17&gt;=1000,0.0474,IF(E17&gt;=300,0.0533,IF(E17&gt;=100,0.0611,0.0769)))))</f>
+        <v>0.0769</v>
       </c>
       <c r="G17" s="32" t="n">
         <f>IF(ISNUMBER(F17),D17*F17,"")</f>
-        <v>0.764</v>
+        <v>0.1538</v>
       </c>
       <c r="H17" s="32" t="n">
         <f>IF(ISNUMBER(F17),E17*F17,"")</f>
-        <v>4.584</v>
+        <v>1.5379999999999998</v>
       </c>
       <c r="I17" s="28" t="n">
-        <v>48511</v>
+        <v>3460</v>
       </c>
       <c r="J17" s="23" t="str">
         <f>IF(ISNUMBER(I17),IF(I17&gt;=E17,"Available","Short stock"),"Unconfirmed")</f>
@@ -3064,7 +3051,7 @@
         <v>32.96</v>
       </c>
       <c r="I40" s="29" t="n">
-        <v>8500</v>
+        <v>7450</v>
       </c>
       <c r="J40" s="25" t="str">
         <f>IF(ISNUMBER(I40),IF(I40&gt;=E40,"Available","Short stock"),"Unconfirmed")</f>
@@ -3406,11 +3393,11 @@
       <c r="F49" s="36"/>
       <c r="G49" s="37" t="n">
         <f>SUM(G9:G48)</f>
-        <v>57.84179999999999</v>
+        <v>57.2316</v>
       </c>
       <c r="H49" s="37" t="n">
         <f>SUM(H9:H48)</f>
-        <v>788.8374</v>
+        <v>785.7914000000002</v>
       </c>
       <c r="I49" s="36"/>
       <c r="J49" s="36"/>
@@ -3709,7 +3696,7 @@
       <c r="G65" s="36"/>
       <c r="H65" s="37" t="n">
         <f>SUM(H9:H48)+SUM(I55:I64)</f>
-        <v>788.8374</v>
+        <v>785.7914000000002</v>
       </c>
       <c r="I65" s="36"/>
       <c r="J65" s="36"/>
@@ -3875,7 +3862,7 @@
     <hyperlink ref="K14" r:id="purchase5" display="View part" tooltip="Open DigiKey part page"/>
     <hyperlink ref="K15" r:id="purchase6" display="View part" tooltip="Open LCSC part page"/>
     <hyperlink ref="K16" r:id="purchase7" display="View part" tooltip="Open LCSC part page"/>
-    <hyperlink ref="K17" r:id="purchase8" display="View part" tooltip="Open DigiKey part page"/>
+    <hyperlink ref="K17" r:id="purchase8" display="View part" tooltip="Open LCSC part page"/>
     <hyperlink ref="K18" r:id="purchase9" display="View part" tooltip="Open DigiKey part page"/>
     <hyperlink ref="K19" r:id="purchase10" display="View part" tooltip="Open DigiKey part page"/>
     <hyperlink ref="K20" r:id="purchase11" display="View part" tooltip="Open DigiKey part page"/>
@@ -3909,6 +3896,6 @@
     <hyperlink ref="K48" r:id="purchase39" display="View part" tooltip="Open DigiKey part page"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="R86445d7649134bfd"/>
+  <legacyDrawing r:id="R88909b3eaf2f4112"/>
 </worksheet>
 </file>